--- a/문서/itemOptionData.xlsx
+++ b/문서/itemOptionData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.286.56066"/>
+  <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="520" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="510" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>idx</t>
   </si>
@@ -219,6 +219,12 @@
   </si>
   <si>
     <t>공격시 +{0}% 확률로 땅을 타는 불꽃 생성</t>
+  </si>
+  <si>
+    <t>1,3</t>
+  </si>
+  <si>
+    <t>[]</t>
   </si>
 </sst>
 </file>
@@ -770,7 +776,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -779,9 +785,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1136,10 +1139,10 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="3">
+      <c r="A2" s="1">
         <v>90001</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="1">
@@ -1162,10 +1165,10 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>90002</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="1">
@@ -1188,10 +1191,10 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="3">
+      <c r="A4" s="1">
         <v>90003</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C4" s="1">
@@ -1214,10 +1217,10 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>90004</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C5" s="1">
@@ -1240,10 +1243,10 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="3">
+      <c r="A6" s="1">
         <v>90005</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="1">
@@ -1266,10 +1269,10 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="3">
+      <c r="A7" s="1">
         <v>90006</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C7" s="1">
@@ -1292,10 +1295,10 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="3">
+      <c r="A8" s="1">
         <v>90007</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C8" s="1">
@@ -1318,10 +1321,10 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="3">
+      <c r="A9" s="1">
         <v>90008</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C9" s="1">
@@ -1344,52 +1347,148 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="3">
+      <c r="A10" s="1">
         <v>90009</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="H10" s="1"/>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="3">
+      <c r="A11" s="1">
         <v>90010</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="H11" s="1"/>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="3">
+      <c r="A12" s="1">
         <v>90011</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="H12" s="1"/>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="3">
+      <c r="A13" s="1">
         <v>90012</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="H13" s="1"/>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="3">
+      <c r="A14" s="1">
         <v>90013</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="H14" s="1"/>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="3">
+      <c r="A15" s="1">
         <v>90014</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="H15" s="1"/>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="3">
+      <c r="A16" s="1">
         <v>90015</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="1">
@@ -1401,8 +1500,8 @@
       <c r="E16" s="1">
         <v>0</v>
       </c>
-      <c r="F16" s="1">
-        <v>0</v>
+      <c r="F16" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1412,10 +1511,10 @@
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="3">
+      <c r="A17" s="1">
         <v>91001</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C17" s="1">
@@ -1438,10 +1537,10 @@
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="3">
+      <c r="A18" s="1">
         <v>91002</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C18" s="1">
@@ -1464,10 +1563,10 @@
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="3">
+      <c r="A19" s="1">
         <v>92000</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="1">
@@ -1479,8 +1578,8 @@
       <c r="E19" s="1">
         <v>0</v>
       </c>
-      <c r="F19" s="1">
-        <v>0</v>
+      <c r="F19" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -1490,10 +1589,10 @@
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="3">
+      <c r="A20" s="1">
         <v>95001</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C20" s="1">
@@ -1505,8 +1604,8 @@
       <c r="E20" s="1">
         <v>0</v>
       </c>
-      <c r="F20" s="1">
-        <v>0</v>
+      <c r="F20" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -1516,16 +1615,50 @@
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="3">
+      <c r="A21" s="1">
         <v>95002</v>
       </c>
-      <c r="B21" s="3"/>
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="3">
+      <c r="A22" s="1">
         <v>95003</v>
       </c>
-      <c r="B22" s="3"/>
+      <c r="C22" s="1">
+        <v>0</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/문서/itemOptionData.xlsx
+++ b/문서/itemOptionData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="510" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="500" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>idx</t>
   </si>
@@ -225,6 +225,15 @@
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>추가 체력 +{0}</t>
+  </si>
+  <si>
+    <t>추가 체력 +{}</t>
+  </si>
+  <si>
+    <t>추가 체력 +{0}% 증가</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="15.62500000" defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
@@ -1564,10 +1573,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>92000</v>
+        <v>92001</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
@@ -1576,47 +1585,50 @@
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>95001</v>
+        <v>92002</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>95002</v>
+        <v>93000</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -1639,7 +1651,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>95003</v>
+        <v>95001</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="C22" s="1">
         <v>0</v>
@@ -1657,6 +1672,52 @@
         <v>0</v>
       </c>
       <c r="H22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1">
+        <v>95002</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1">
+        <v>95003</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
         <v>0</v>
       </c>
     </row>
